--- a/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
+++ b/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/reporting-and-kpis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/ticketing-system/reporting-and-kpis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="414" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F6C8E2D-7BA1-47B8-BD07-2AB1674D1C6E}"/>
+  <xr:revisionPtr revIDLastSave="415" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61E7F1D2-674D-4634-8DBA-7105608C1AD5}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="16515" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5340" yWindow="2325" windowWidth="16515" windowHeight="16380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="11" r:id="rId1"/>
@@ -413,6 +413,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+  </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -571,7 +574,6 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -598,6 +600,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Heading 1" xfId="1" builtinId="16" hidden="1"/>
@@ -606,6 +609,18 @@
     <cellStyle name="Title" xfId="2" builtinId="15" hidden="1"/>
   </cellStyles>
   <dxfs count="47">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -631,73 +646,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <fill>
@@ -770,6 +719,60 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1869,10 +1872,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="austin webber" refreshedDate="46162.590005902777" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="15" xr:uid="{9D7E426B-AAB8-49CA-A43C-947026B00E61}">
   <cacheSource type="worksheet">
@@ -2426,186 +2425,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A16:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item n="Open / Unresolved" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="17"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="17">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="16">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="22">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="19">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
@@ -2682,19 +2501,19 @@
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="27">
+    <format dxfId="17">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="14">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -2721,7 +2540,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I5:M11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="20">
@@ -2802,39 +2621,203 @@
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="36">
+    <format dxfId="26">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="23">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="22">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="19">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E16:F19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="31">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
     <format dxfId="28">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A16:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item n="Open / Unresolved" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="17"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="36">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -2851,8 +2834,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E16:F19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
@@ -2863,10 +2846,12 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="3">
+      <items count="7">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
@@ -2880,16 +2865,30 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="11"/>
+    <field x="9"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="7">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -2964,16 +2963,16 @@
   <autoFilter ref="A1:T16" xr:uid="{DE97B8D0-E5C6-4059-B16C-616CFCE9AC0E}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{09E599F5-5DC2-4648-A8A2-3111DB7D97E8}" uniqueName="1" name="ticket_id" queryTableFieldId="1" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{66E46FE5-2BF1-4C00-88E5-BADA26B9AD28}" uniqueName="2" name="created_at" queryTableFieldId="2" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{E589D37C-991B-4D9E-8734-2A39C3145538}" uniqueName="3" name="first_response_at" queryTableFieldId="3" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{7CD77852-F46B-467B-8F18-B8CF225E34EF}" uniqueName="4" name="resolved_at" queryTableFieldId="4" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{8A165E11-8702-4BDC-97B8-558593A55025}" uniqueName="5" name="closed_at" queryTableFieldId="5" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{E9645A80-61A8-4CD1-868F-D804A78A41CF}" uniqueName="6" name="category" queryTableFieldId="6" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{B8A06DA3-47F1-4B26-B454-02C191521227}" uniqueName="7" name="priority" queryTableFieldId="7" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{30CC1504-542F-449A-A047-1DB5FA48F4E2}" uniqueName="8" name="status" queryTableFieldId="8" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{11402AD9-AD11-4921-B6F7-2A3397C40B72}" uniqueName="9" name="requesting_location" queryTableFieldId="9" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{E8EDD650-D31C-4F64-AA3D-F6D196B1943F}" uniqueName="10" name="assigned_department" queryTableFieldId="10" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{CBF6C16E-143B-4589-8269-54E88A2E69A4}" uniqueName="11" name="assigned_owner" queryTableFieldId="11" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{66E46FE5-2BF1-4C00-88E5-BADA26B9AD28}" uniqueName="2" name="created_at" queryTableFieldId="2" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{E589D37C-991B-4D9E-8734-2A39C3145538}" uniqueName="3" name="first_response_at" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{7CD77852-F46B-467B-8F18-B8CF225E34EF}" uniqueName="4" name="resolved_at" queryTableFieldId="4" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{8A165E11-8702-4BDC-97B8-558593A55025}" uniqueName="5" name="closed_at" queryTableFieldId="5" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{E9645A80-61A8-4CD1-868F-D804A78A41CF}" uniqueName="6" name="category" queryTableFieldId="6" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{B8A06DA3-47F1-4B26-B454-02C191521227}" uniqueName="7" name="priority" queryTableFieldId="7" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{30CC1504-542F-449A-A047-1DB5FA48F4E2}" uniqueName="8" name="status" queryTableFieldId="8" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{11402AD9-AD11-4921-B6F7-2A3397C40B72}" uniqueName="9" name="requesting_location" queryTableFieldId="9" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{E8EDD650-D31C-4F64-AA3D-F6D196B1943F}" uniqueName="10" name="assigned_department" queryTableFieldId="10" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{CBF6C16E-143B-4589-8269-54E88A2E69A4}" uniqueName="11" name="assigned_owner" queryTableFieldId="11" dataDxfId="6"/>
     <tableColumn id="12" xr3:uid="{333F9053-52CE-4692-B0D9-936E0734A9AD}" uniqueName="12" name="escalation_flag" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{C5C46961-D093-4C40-9DAE-60DCFCA7D500}" uniqueName="13" name="reopened_flag" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{F488B704-C567-4436-B6A8-01C4AD19592F}" uniqueName="14" name="pending_flag" queryTableFieldId="14"/>
@@ -2981,8 +2980,8 @@
     <tableColumn id="16" xr3:uid="{62724D38-EBC7-42AA-B061-AB26F0B655B8}" uniqueName="16" name="resolution_hours" queryTableFieldId="16"/>
     <tableColumn id="17" xr3:uid="{BDBE98A7-7B7B-4058-95A6-4FBCD833FF06}" uniqueName="17" name="response_hours" queryTableFieldId="17"/>
     <tableColumn id="18" xr3:uid="{26B2574B-E442-49CA-9FE5-20E5CD3D80CF}" uniqueName="18" name="sla_met_flag" queryTableFieldId="18"/>
-    <tableColumn id="19" xr3:uid="{21856449-41DC-4B1B-A0D6-C8627B60B080}" uniqueName="19" name="summary" queryTableFieldId="19" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{3AD83A7D-C03B-4A45-BC8F-FB5901509577}" uniqueName="20" name="resolution_notes" queryTableFieldId="20" dataDxfId="0"/>
+    <tableColumn id="19" xr3:uid="{21856449-41DC-4B1B-A0D6-C8627B60B080}" uniqueName="19" name="summary" queryTableFieldId="19" dataDxfId="5"/>
+    <tableColumn id="20" xr3:uid="{3AD83A7D-C03B-4A45-BC8F-FB5901509577}" uniqueName="20" name="resolution_notes" queryTableFieldId="20" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3259,73 +3258,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
+      <c r="A2" s="6"/>
     </row>
     <row r="3" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
+      <c r="A6" s="7"/>
     </row>
     <row r="8" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3350,91 +3349,91 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="26" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="12"/>
+      <c r="B27" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
+      <c r="A38" s="9"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -3457,13 +3456,13 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3490,295 +3489,295 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="5" t="s">
+      <c r="I6" s="12"/>
+      <c r="J6" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>3</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>1</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>1</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3">
+      <c r="L7" s="2"/>
+      <c r="M7" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>3</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>1</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>2</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <v>2</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>2</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>3</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>3</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3">
+      <c r="J9" s="2"/>
+      <c r="K9" s="2">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>1</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>3</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3">
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2">
         <v>1</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>3</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="4">
         <v>8</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="4">
         <v>4</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>15</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="E13" s="1"/>
     </row>
     <row r="15" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="11"/>
+      <c r="I15" s="10"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5" t="s">
+      <c r="E16" s="3"/>
+      <c r="F16" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <v>3</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <v>8</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <v>4</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+      <c r="A21" s="1"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="A23" s="10"/>
+      <c r="F23" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3793,9 +3792,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.5703125" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -3816,16 +3815,16 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -3878,16 +3877,16 @@
       <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="17">
         <v>46162.341666666667</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="17">
         <v>46162.35</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="17">
         <v>46162.447916666664</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="17">
         <v>46162.459722222222</v>
       </c>
       <c r="F2" t="s">
@@ -3940,16 +3939,16 @@
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="17">
         <v>46162.377083333333</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="17">
         <v>46162.402777777781</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="17">
         <v>46163.59375</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="17">
         <v>46163.612500000003</v>
       </c>
       <c r="F3" t="s">
@@ -4002,16 +4001,16 @@
       <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="17">
         <v>46162.424305555556</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="17">
         <v>46162.436805555553</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="17">
         <v>46162.574999999997</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="17">
         <v>46162.585416666669</v>
       </c>
       <c r="F4" t="s">
@@ -4064,14 +4063,12 @@
       <c r="A5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="17">
         <v>46162.476388888892</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="17">
         <v>46162.496527777781</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
       <c r="F5" t="s">
         <v>45</v>
       </c>
@@ -4116,16 +4113,16 @@
       <c r="A6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="17">
         <v>46162.554166666669</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="17">
         <v>46162.577777777777</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="17">
         <v>46163.384722222225</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="17">
         <v>46163.402777777781</v>
       </c>
       <c r="F6" t="s">
@@ -4178,16 +4175,16 @@
       <c r="A7" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="17">
         <v>46162.584722222222</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="17">
         <v>46162.600694444445</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="17">
         <v>46162.679166666669</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="17">
         <v>46162.694444444445</v>
       </c>
       <c r="F7" t="s">
@@ -4240,14 +4237,12 @@
       <c r="A8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="17">
         <v>46162.655555555553</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="17">
         <v>46162.686111111114</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
       <c r="F8" t="s">
         <v>30</v>
       </c>
@@ -4292,16 +4287,16 @@
       <c r="A9" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="17">
         <v>46162.677083333336</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="17">
         <v>46162.695138888892</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="17">
         <v>46162.751388888886</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="17">
         <v>46162.762499999997</v>
       </c>
       <c r="F9" t="s">
@@ -4354,16 +4349,16 @@
       <c r="A10" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="17">
         <v>46162.730555555558</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="17">
         <v>46162.756944444445</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="17">
         <v>46163.362500000003</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="17">
         <v>46163.382638888892</v>
       </c>
       <c r="F10" t="s">
@@ -4416,16 +4411,16 @@
       <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="17">
         <v>46162.75277777778</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="17">
         <v>46162.78125</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="17">
         <v>46164.470833333333</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="17">
         <v>46164.490972222222</v>
       </c>
       <c r="F11" t="s">
@@ -4478,16 +4473,16 @@
       <c r="A12" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="17">
         <v>46163.304166666669</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="17">
         <v>46163.320833333331</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="17">
         <v>46163.380555555559</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="17">
         <v>46163.393055555556</v>
       </c>
       <c r="F12" t="s">
@@ -4540,14 +4535,12 @@
       <c r="A13" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="17">
         <v>46163.34097222222</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="17">
         <v>46163.371527777781</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
       <c r="F13" t="s">
         <v>21</v>
       </c>
@@ -4592,16 +4585,16 @@
       <c r="A14" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="17">
         <v>46163.405555555553</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="17">
         <v>46163.429166666669</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="17">
         <v>46163.54791666667</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="17">
         <v>46163.56527777778</v>
       </c>
       <c r="F14" t="s">
@@ -4654,16 +4647,16 @@
       <c r="A15" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="17">
         <v>46163.452777777777</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="17">
         <v>46163.48541666667</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="17">
         <v>46164.654166666667</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="17">
         <v>46164.673611111109</v>
       </c>
       <c r="F15" t="s">
@@ -4716,14 +4709,12 @@
       <c r="A16" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="17">
         <v>46163.481249999997</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="17">
         <v>46163.501388888886</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
       <c r="F16" t="s">
         <v>45</v>
       </c>

--- a/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
+++ b/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/ticketing-system/reporting-and-kpis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="415" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61E7F1D2-674D-4634-8DBA-7105608C1AD5}"/>
+  <xr:revisionPtr revIDLastSave="419" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83FA75E0-C8C0-48C5-8B2F-42CC21AA690E}"/>
   <bookViews>
-    <workbookView xWindow="5340" yWindow="2325" windowWidth="16515" windowHeight="16380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2685" yWindow="2685" windowWidth="16515" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="11" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="19" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -572,7 +572,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -601,6 +601,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Heading 1" xfId="1" builtinId="16" hidden="1"/>
@@ -609,45 +610,6 @@
     <cellStyle name="Title" xfId="2" builtinId="15" hidden="1"/>
   </cellStyles>
   <dxfs count="47">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -668,57 +630,6 @@
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -829,10 +740,100 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1872,6 +1873,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="austin webber" refreshedDate="46162.590005902777" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="15" xr:uid="{9D7E426B-AAB8-49CA-A43C-947026B00E61}">
   <cacheSource type="worksheet">
@@ -2309,7 +2314,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1C50735-BA19-4163-9127-F01340C7EAE1}" name="PivotTable16" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1C50735-BA19-4163-9127-F01340C7EAE1}" name="PivotTable16" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A27:B34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
@@ -2385,19 +2390,19 @@
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="46">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="30">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -2425,7 +2430,267 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E16:F19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A16:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item n="Open / Unresolved" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="17"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="9">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="14">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
@@ -2501,19 +2766,19 @@
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="17">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="16">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -2540,8 +2805,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I5:M11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
@@ -2621,299 +2886,39 @@
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="26">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="25">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="24">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="21">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E16:F19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="31">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="28">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="27">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A16:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item n="Open / Unresolved" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="17"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="36">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="41">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="40">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="39">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="38">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -2962,17 +2967,17 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE97B8D0-E5C6-4059-B16C-616CFCE9AC0E}" name="tickets_v1" displayName="tickets_v1" ref="A1:T16" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:T16" xr:uid="{DE97B8D0-E5C6-4059-B16C-616CFCE9AC0E}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{09E599F5-5DC2-4648-A8A2-3111DB7D97E8}" uniqueName="1" name="ticket_id" queryTableFieldId="1" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{66E46FE5-2BF1-4C00-88E5-BADA26B9AD28}" uniqueName="2" name="created_at" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{E589D37C-991B-4D9E-8734-2A39C3145538}" uniqueName="3" name="first_response_at" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{7CD77852-F46B-467B-8F18-B8CF225E34EF}" uniqueName="4" name="resolved_at" queryTableFieldId="4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{8A165E11-8702-4BDC-97B8-558593A55025}" uniqueName="5" name="closed_at" queryTableFieldId="5" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{E9645A80-61A8-4CD1-868F-D804A78A41CF}" uniqueName="6" name="category" queryTableFieldId="6" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{B8A06DA3-47F1-4B26-B454-02C191521227}" uniqueName="7" name="priority" queryTableFieldId="7" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{30CC1504-542F-449A-A047-1DB5FA48F4E2}" uniqueName="8" name="status" queryTableFieldId="8" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{11402AD9-AD11-4921-B6F7-2A3397C40B72}" uniqueName="9" name="requesting_location" queryTableFieldId="9" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{E8EDD650-D31C-4F64-AA3D-F6D196B1943F}" uniqueName="10" name="assigned_department" queryTableFieldId="10" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{CBF6C16E-143B-4589-8269-54E88A2E69A4}" uniqueName="11" name="assigned_owner" queryTableFieldId="11" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{09E599F5-5DC2-4648-A8A2-3111DB7D97E8}" uniqueName="1" name="ticket_id" queryTableFieldId="1" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{66E46FE5-2BF1-4C00-88E5-BADA26B9AD28}" uniqueName="2" name="created_at" queryTableFieldId="2" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{E589D37C-991B-4D9E-8734-2A39C3145538}" uniqueName="3" name="first_response_at" queryTableFieldId="3" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{7CD77852-F46B-467B-8F18-B8CF225E34EF}" uniqueName="4" name="resolved_at" queryTableFieldId="4" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{8A165E11-8702-4BDC-97B8-558593A55025}" uniqueName="5" name="closed_at" queryTableFieldId="5" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{E9645A80-61A8-4CD1-868F-D804A78A41CF}" uniqueName="6" name="category" queryTableFieldId="6" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{B8A06DA3-47F1-4B26-B454-02C191521227}" uniqueName="7" name="priority" queryTableFieldId="7" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{30CC1504-542F-449A-A047-1DB5FA48F4E2}" uniqueName="8" name="status" queryTableFieldId="8" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{11402AD9-AD11-4921-B6F7-2A3397C40B72}" uniqueName="9" name="requesting_location" queryTableFieldId="9" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{E8EDD650-D31C-4F64-AA3D-F6D196B1943F}" uniqueName="10" name="assigned_department" queryTableFieldId="10" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{CBF6C16E-143B-4589-8269-54E88A2E69A4}" uniqueName="11" name="assigned_owner" queryTableFieldId="11" dataDxfId="36"/>
     <tableColumn id="12" xr3:uid="{333F9053-52CE-4692-B0D9-936E0734A9AD}" uniqueName="12" name="escalation_flag" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{C5C46961-D093-4C40-9DAE-60DCFCA7D500}" uniqueName="13" name="reopened_flag" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{F488B704-C567-4436-B6A8-01C4AD19592F}" uniqueName="14" name="pending_flag" queryTableFieldId="14"/>
@@ -2980,8 +2985,8 @@
     <tableColumn id="16" xr3:uid="{62724D38-EBC7-42AA-B061-AB26F0B655B8}" uniqueName="16" name="resolution_hours" queryTableFieldId="16"/>
     <tableColumn id="17" xr3:uid="{BDBE98A7-7B7B-4058-95A6-4FBCD833FF06}" uniqueName="17" name="response_hours" queryTableFieldId="17"/>
     <tableColumn id="18" xr3:uid="{26B2574B-E442-49CA-9FE5-20E5CD3D80CF}" uniqueName="18" name="sla_met_flag" queryTableFieldId="18"/>
-    <tableColumn id="19" xr3:uid="{21856449-41DC-4B1B-A0D6-C8627B60B080}" uniqueName="19" name="summary" queryTableFieldId="19" dataDxfId="5"/>
-    <tableColumn id="20" xr3:uid="{3AD83A7D-C03B-4A45-BC8F-FB5901509577}" uniqueName="20" name="resolution_notes" queryTableFieldId="20" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{21856449-41DC-4B1B-A0D6-C8627B60B080}" uniqueName="19" name="summary" queryTableFieldId="19" dataDxfId="35"/>
+    <tableColumn id="20" xr3:uid="{3AD83A7D-C03B-4A45-BC8F-FB5901509577}" uniqueName="20" name="resolution_notes" queryTableFieldId="20" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3250,7 +3255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A55D82-B18D-478C-8743-BB6B0E9B43B7}">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -3323,55 +3328,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-    </row>
-    <row r="26" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:2" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
@@ -3379,7 +3378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>45</v>
       </c>
@@ -3387,7 +3386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>21</v>
       </c>
@@ -3395,7 +3394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>51</v>
       </c>
@@ -3403,7 +3402,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
@@ -3411,7 +3410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -3419,7 +3418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>90</v>
       </c>
@@ -3427,43 +3426,40 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+    <row r="43" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-    </row>
+    </row>
+    <row r="44" spans="1:2" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId2"/>

--- a/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
+++ b/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/ticketing-system/reporting-and-kpis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83FA75E0-C8C0-48C5-8B2F-42CC21AA690E}"/>
+  <xr:revisionPtr revIDLastSave="521" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC8D9550-280C-499B-9FAE-045DB0C66A77}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2685" yWindow="2685" windowWidth="16515" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="11" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId4"/>
+    <pivotCache cacheId="5" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="131">
   <si>
     <t>ticket_id</t>
   </si>
@@ -313,15 +313,6 @@
     <t>Historical reporting documentation request submitted for compliance review</t>
   </si>
   <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>FALSE</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
     <t>Ticket Volume by Category</t>
   </si>
   <si>
@@ -346,21 +337,12 @@
     <t>Northstar Health Operations</t>
   </si>
   <si>
-    <t>Operational KPI Executive Summary</t>
-  </si>
-  <si>
-    <t>Reporting Period: May 20–21, 2026</t>
-  </si>
-  <si>
     <t>Operational KPI Highlights</t>
   </si>
   <si>
     <t>Total Operational Tickets</t>
   </si>
   <si>
-    <t>Open / Unresovled Tickets</t>
-  </si>
-  <si>
     <t>Escalated Tickets</t>
   </si>
   <si>
@@ -407,6 +389,62 @@
   </si>
   <si>
     <t>• Continue monitoring SLA performance trends for escalated operational workflows.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Purpose: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Provide a high-level overview of ticket volume, service performance, escalation activity, and operational conditions during the reporting period.</t>
+    </r>
+  </si>
+  <si>
+    <t>Reporting Period: May 2026</t>
+  </si>
+  <si>
+    <t>Open / Unresolved Tickets</t>
+  </si>
+  <si>
+    <t>Executive Summary</t>
+  </si>
+  <si>
+    <t>Recommended Focus Areas</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>The report is based on complete ticket activity captured during the reporting period. KPI calculations and observations are supported by the available operational data.</t>
+  </si>
+  <si>
+    <t>SLA Not Met</t>
+  </si>
+  <si>
+    <t>SLA Met</t>
+  </si>
+  <si>
+    <t>Not Escalated</t>
+  </si>
+  <si>
+    <t>Escalated</t>
+  </si>
+  <si>
+    <t>• Inventory, vendor, and operational incidents account for most ticket activity. Continued monitoring may help identify recurring process bottlenecks within high-volume categories.</t>
+  </si>
+  <si>
+    <t>• Critical and high-priority tickets experienced the highest rate of SLA failures. Response performance for high-impact incidents should continue to be monitored.</t>
+  </si>
+  <si>
+    <t>• Most completed tickets met SLA targets. Open and unresolved tickets should be monitored to reduce future compliance risk.</t>
+  </si>
+  <si>
+    <t>• One-third of ticket activity required escalation. Elevated escalation volume may indicate workflow dependencies or operational friction points.</t>
   </si>
 </sst>
 </file>
@@ -416,7 +454,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,6 +553,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -530,7 +574,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -565,6 +609,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -572,19 +687,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -593,7 +698,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" pivotButton="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -601,7 +705,46 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Heading 1" xfId="1" builtinId="16" hidden="1"/>
@@ -609,7 +752,110 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="2" builtinId="15" hidden="1"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="59">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -638,6 +884,70 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -665,6 +975,70 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -692,6 +1066,22 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -713,12 +1103,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -740,6 +1124,79 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -765,75 +1222,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1012,7 +1400,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Tables'!$A$6:$A$12</c:f>
+              <c:f>'Pivot Tables'!$A$6:$A$11</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1038,7 +1426,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Tables'!$B$6:$B$12</c:f>
+              <c:f>'Pivot Tables'!$B$6:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1838,13 +2226,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2314,8 +2702,214 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1C50735-BA19-4163-9127-F01340C7EAE1}" name="PivotTable16" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A27:B34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item n="SLA Not Met" x="1"/>
+        <item n="SLA Met" x="0"/>
+        <item n="Open / Unresolved" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="17"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="30">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A5:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
@@ -2360,7 +2954,7 @@
   <rowFields count="1">
     <field x="5"/>
   </rowFields>
-  <rowItems count="7">
+  <rowItems count="6">
     <i>
       <x v="5"/>
     </i>
@@ -2379,9 +2973,6 @@
     <i>
       <x v="4"/>
     </i>
-    <i t="grand">
-      <x/>
-    </i>
   </rowItems>
   <colItems count="1">
     <i/>
@@ -2389,21 +2980,37 @@
   <dataFields count="1">
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="5">
+  <formats count="9">
+    <format dxfId="39">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
     <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
     </format>
     <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="30">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
   <chartFormats count="1">
@@ -2429,9 +3036,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E16:F19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I5:L10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
@@ -2439,15 +3046,12 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="3">
+      <items count="5">
+        <item x="2"/>
         <item x="0"/>
         <item x="1"/>
+        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2459,81 +3063,12 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="4">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A16:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
       <items count="4">
-        <item x="1"/>
-        <item x="0"/>
+        <item n="SLA Not Met" x="1"/>
+        <item n="SLA Met" x="0"/>
         <item n="Open / Unresolved" x="2"/>
         <item t="default"/>
       </items>
@@ -2542,96 +3077,9 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="17"/>
+    <field x="6"/>
   </rowFields>
   <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="9">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="7">
     <i>
       <x/>
     </i>
@@ -2644,37 +3092,62 @@
     <i>
       <x v="3"/>
     </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="3">
     <i>
-      <x v="4"/>
+      <x/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="1"/>
     </i>
-    <i t="grand">
-      <x/>
+    <i>
+      <x v="2"/>
     </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
   </colItems>
   <dataFields count="1">
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="5">
-    <format dxfId="14">
+  <formats count="10">
+    <format dxfId="49">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    <format dxfId="48">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
     </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="46">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="43">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="40">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -2690,40 +3163,27 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E18:F20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item n="Not Escalated" x="0"/>
+        <item n="Escalated" x="1"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2734,29 +3194,14 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="5"/>
+    <field x="11"/>
   </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="5"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -2765,161 +3210,37 @@
   <dataFields count="1">
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="5">
-    <format dxfId="19">
+  <formats count="9">
+    <format dxfId="58">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="55">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="I5:M11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item n="Open / Unresolved" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="28">
+    <format dxfId="53">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="17" count="0"/>
+          <reference field="11" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="25">
-      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -2967,17 +3288,17 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE97B8D0-E5C6-4059-B16C-616CFCE9AC0E}" name="tickets_v1" displayName="tickets_v1" ref="A1:T16" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:T16" xr:uid="{DE97B8D0-E5C6-4059-B16C-616CFCE9AC0E}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{09E599F5-5DC2-4648-A8A2-3111DB7D97E8}" uniqueName="1" name="ticket_id" queryTableFieldId="1" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{66E46FE5-2BF1-4C00-88E5-BADA26B9AD28}" uniqueName="2" name="created_at" queryTableFieldId="2" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{E589D37C-991B-4D9E-8734-2A39C3145538}" uniqueName="3" name="first_response_at" queryTableFieldId="3" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{7CD77852-F46B-467B-8F18-B8CF225E34EF}" uniqueName="4" name="resolved_at" queryTableFieldId="4" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{8A165E11-8702-4BDC-97B8-558593A55025}" uniqueName="5" name="closed_at" queryTableFieldId="5" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{E9645A80-61A8-4CD1-868F-D804A78A41CF}" uniqueName="6" name="category" queryTableFieldId="6" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{B8A06DA3-47F1-4B26-B454-02C191521227}" uniqueName="7" name="priority" queryTableFieldId="7" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{30CC1504-542F-449A-A047-1DB5FA48F4E2}" uniqueName="8" name="status" queryTableFieldId="8" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{11402AD9-AD11-4921-B6F7-2A3397C40B72}" uniqueName="9" name="requesting_location" queryTableFieldId="9" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{E8EDD650-D31C-4F64-AA3D-F6D196B1943F}" uniqueName="10" name="assigned_department" queryTableFieldId="10" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{CBF6C16E-143B-4589-8269-54E88A2E69A4}" uniqueName="11" name="assigned_owner" queryTableFieldId="11" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{09E599F5-5DC2-4648-A8A2-3111DB7D97E8}" uniqueName="1" name="ticket_id" queryTableFieldId="1" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{66E46FE5-2BF1-4C00-88E5-BADA26B9AD28}" uniqueName="2" name="created_at" queryTableFieldId="2" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{E589D37C-991B-4D9E-8734-2A39C3145538}" uniqueName="3" name="first_response_at" queryTableFieldId="3" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{7CD77852-F46B-467B-8F18-B8CF225E34EF}" uniqueName="4" name="resolved_at" queryTableFieldId="4" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{8A165E11-8702-4BDC-97B8-558593A55025}" uniqueName="5" name="closed_at" queryTableFieldId="5" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{E9645A80-61A8-4CD1-868F-D804A78A41CF}" uniqueName="6" name="category" queryTableFieldId="6" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{B8A06DA3-47F1-4B26-B454-02C191521227}" uniqueName="7" name="priority" queryTableFieldId="7" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{30CC1504-542F-449A-A047-1DB5FA48F4E2}" uniqueName="8" name="status" queryTableFieldId="8" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{11402AD9-AD11-4921-B6F7-2A3397C40B72}" uniqueName="9" name="requesting_location" queryTableFieldId="9" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{E8EDD650-D31C-4F64-AA3D-F6D196B1943F}" uniqueName="10" name="assigned_department" queryTableFieldId="10" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{CBF6C16E-143B-4589-8269-54E88A2E69A4}" uniqueName="11" name="assigned_owner" queryTableFieldId="11" dataDxfId="2"/>
     <tableColumn id="12" xr3:uid="{333F9053-52CE-4692-B0D9-936E0734A9AD}" uniqueName="12" name="escalation_flag" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{C5C46961-D093-4C40-9DAE-60DCFCA7D500}" uniqueName="13" name="reopened_flag" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{F488B704-C567-4436-B6A8-01C4AD19592F}" uniqueName="14" name="pending_flag" queryTableFieldId="14"/>
@@ -2985,8 +3306,8 @@
     <tableColumn id="16" xr3:uid="{62724D38-EBC7-42AA-B061-AB26F0B655B8}" uniqueName="16" name="resolution_hours" queryTableFieldId="16"/>
     <tableColumn id="17" xr3:uid="{BDBE98A7-7B7B-4058-95A6-4FBCD833FF06}" uniqueName="17" name="response_hours" queryTableFieldId="17"/>
     <tableColumn id="18" xr3:uid="{26B2574B-E442-49CA-9FE5-20E5CD3D80CF}" uniqueName="18" name="sla_met_flag" queryTableFieldId="18"/>
-    <tableColumn id="19" xr3:uid="{21856449-41DC-4B1B-A0D6-C8627B60B080}" uniqueName="19" name="summary" queryTableFieldId="19" dataDxfId="35"/>
-    <tableColumn id="20" xr3:uid="{3AD83A7D-C03B-4A45-BC8F-FB5901509577}" uniqueName="20" name="resolution_notes" queryTableFieldId="20" dataDxfId="34"/>
+    <tableColumn id="19" xr3:uid="{21856449-41DC-4B1B-A0D6-C8627B60B080}" uniqueName="19" name="summary" queryTableFieldId="19" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{3AD83A7D-C03B-4A45-BC8F-FB5901509577}" uniqueName="20" name="resolution_notes" queryTableFieldId="20" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3255,7 +3576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A55D82-B18D-478C-8743-BB6B0E9B43B7}">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -3263,212 +3584,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="10" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6"/>
-    </row>
-    <row r="3" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="B14" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="B15" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-    </row>
-    <row r="8" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="B16" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>105</v>
       </c>
-      <c r="B11" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="26" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+    </row>
+    <row r="29" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+    </row>
+    <row r="39" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="40" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A33:D33"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC74A6B5-0DBE-48E8-96B1-F4D3B84797B7}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.42578125" customWidth="1"/>
@@ -3476,306 +3762,284 @@
     <col min="3" max="3" width="8.42578125" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="30.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
     <col min="7" max="7" width="6.7109375" customWidth="1"/>
     <col min="8" max="8" width="5.7109375" customWidth="1"/>
     <col min="9" max="9" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="20"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="16">
+        <v>3</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="16">
+        <v>2</v>
+      </c>
+      <c r="I6" s="21"/>
+      <c r="J6" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="16">
+        <v>3</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="16">
+        <v>3</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="24">
+        <v>1</v>
+      </c>
+      <c r="K7" s="24">
+        <v>1</v>
+      </c>
+      <c r="L7" s="16"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="16">
+        <v>3</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="24">
+        <v>2</v>
+      </c>
+      <c r="K8" s="24">
+        <v>2</v>
+      </c>
+      <c r="L8" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="16">
+        <v>3</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="16">
+        <v>3</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24">
+        <v>5</v>
+      </c>
+      <c r="L9" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="16">
+        <v>2</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="16">
+        <v>3</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="18">
+        <v>1</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="27"/>
+      <c r="E13" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="27"/>
+      <c r="I13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="17" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="J5" s="12"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="16">
         <v>3</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="2">
-        <v>2</v>
-      </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="2">
-        <v>3</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="2">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2">
-        <v>2</v>
-      </c>
-      <c r="K8" s="2">
-        <v>2</v>
-      </c>
-      <c r="L8" s="2">
-        <v>2</v>
-      </c>
-      <c r="M8" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="2">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="2">
-        <v>3</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2">
+      <c r="E19" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" s="16">
+        <v>8</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="18">
         <v>5</v>
       </c>
-      <c r="L9" s="2">
-        <v>1</v>
-      </c>
-      <c r="M9" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="2">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2">
-        <v>1</v>
-      </c>
-      <c r="M10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="2">
-        <v>3</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="J11" s="4">
-        <v>3</v>
-      </c>
-      <c r="K11" s="4">
-        <v>8</v>
-      </c>
-      <c r="L11" s="4">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="18">
         <v>4</v>
       </c>
-      <c r="M11" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" s="4">
-        <v>15</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="15" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="2">
-        <v>3</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="2">
-        <v>8</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="2">
-        <v>4</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
-      <c r="F23" s="10"/>
+    </row>
+    <row r="23" spans="1:9" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="E23" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" s="27"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="27" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="F27" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E23:F23"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId6"/>
   <drawing r:id="rId7"/>
@@ -3788,9 +4052,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -3811,16 +4075,16 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -3873,16 +4137,16 @@
       <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="12">
         <v>46162.341666666667</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="12">
         <v>46162.35</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="12">
         <v>46162.447916666664</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="12">
         <v>46162.459722222222</v>
       </c>
       <c r="F2" t="s">
@@ -3935,16 +4199,16 @@
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="12">
         <v>46162.377083333333</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="12">
         <v>46162.402777777781</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="12">
         <v>46163.59375</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="12">
         <v>46163.612500000003</v>
       </c>
       <c r="F3" t="s">
@@ -3997,16 +4261,16 @@
       <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="12">
         <v>46162.424305555556</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="12">
         <v>46162.436805555553</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="12">
         <v>46162.574999999997</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="12">
         <v>46162.585416666669</v>
       </c>
       <c r="F4" t="s">
@@ -4059,10 +4323,10 @@
       <c r="A5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="12">
         <v>46162.476388888892</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="12">
         <v>46162.496527777781</v>
       </c>
       <c r="F5" t="s">
@@ -4109,16 +4373,16 @@
       <c r="A6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="12">
         <v>46162.554166666669</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="12">
         <v>46162.577777777777</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="12">
         <v>46163.384722222225</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="12">
         <v>46163.402777777781</v>
       </c>
       <c r="F6" t="s">
@@ -4171,16 +4435,16 @@
       <c r="A7" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="12">
         <v>46162.584722222222</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="12">
         <v>46162.600694444445</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="12">
         <v>46162.679166666669</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="12">
         <v>46162.694444444445</v>
       </c>
       <c r="F7" t="s">
@@ -4233,10 +4497,10 @@
       <c r="A8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="12">
         <v>46162.655555555553</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="12">
         <v>46162.686111111114</v>
       </c>
       <c r="F8" t="s">
@@ -4283,16 +4547,16 @@
       <c r="A9" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="12">
         <v>46162.677083333336</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="12">
         <v>46162.695138888892</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="12">
         <v>46162.751388888886</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="12">
         <v>46162.762499999997</v>
       </c>
       <c r="F9" t="s">
@@ -4345,16 +4609,16 @@
       <c r="A10" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="12">
         <v>46162.730555555558</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="12">
         <v>46162.756944444445</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="12">
         <v>46163.362500000003</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="12">
         <v>46163.382638888892</v>
       </c>
       <c r="F10" t="s">
@@ -4407,16 +4671,16 @@
       <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="12">
         <v>46162.75277777778</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="12">
         <v>46162.78125</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="12">
         <v>46164.470833333333</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="12">
         <v>46164.490972222222</v>
       </c>
       <c r="F11" t="s">
@@ -4469,16 +4733,16 @@
       <c r="A12" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="12">
         <v>46163.304166666669</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="12">
         <v>46163.320833333331</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="12">
         <v>46163.380555555559</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="12">
         <v>46163.393055555556</v>
       </c>
       <c r="F12" t="s">
@@ -4531,10 +4795,10 @@
       <c r="A13" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="12">
         <v>46163.34097222222</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="12">
         <v>46163.371527777781</v>
       </c>
       <c r="F13" t="s">
@@ -4581,16 +4845,16 @@
       <c r="A14" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="12">
         <v>46163.405555555553</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="12">
         <v>46163.429166666669</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="12">
         <v>46163.54791666667</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="12">
         <v>46163.56527777778</v>
       </c>
       <c r="F14" t="s">
@@ -4643,16 +4907,16 @@
       <c r="A15" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="12">
         <v>46163.452777777777</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="12">
         <v>46163.48541666667</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="12">
         <v>46164.654166666667</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="12">
         <v>46164.673611111109</v>
       </c>
       <c r="F15" t="s">
@@ -4705,10 +4969,10 @@
       <c r="A16" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="12">
         <v>46163.481249999997</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="12">
         <v>46163.501388888886</v>
       </c>
       <c r="F16" t="s">

--- a/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
+++ b/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/ticketing-system/reporting-and-kpis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="521" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC8D9550-280C-499B-9FAE-045DB0C66A77}"/>
+  <xr:revisionPtr revIDLastSave="522" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD6885BA-3C94-4C38-A489-D352901DA6D7}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1290" windowWidth="23475" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="11" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -687,7 +687,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -737,13 +737,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -900,54 +897,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -969,76 +918,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -1066,6 +945,57 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color indexed="64"/>
@@ -1103,6 +1033,76 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -1122,9 +1122,6 @@
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -2702,41 +2699,56 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A5:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item n="SLA Not Met" x="1"/>
-        <item n="SLA Met" x="0"/>
-        <item n="Open / Unresolved" x="2"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="17"/>
+    <field x="5"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="6">
+    <i>
+      <x v="5"/>
+    </i>
     <i>
       <x/>
     </i>
@@ -2745,6 +2757,12 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -2778,238 +2796,11 @@
     <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="17" count="0"/>
+          <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
     <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="30">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="28">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="27">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="26">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="25">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A5:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="39">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="38">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -3036,8 +2827,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I5:L10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
@@ -3111,42 +2902,42 @@
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="49">
+    <format dxfId="31">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="28">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="27">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="24">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="22">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3162,8 +2953,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E18:F20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
@@ -3202,6 +2993,212 @@
     </i>
     <i>
       <x v="1"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="40">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="39">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="11" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item n="SLA Not Met" x="1"/>
+        <item n="SLA Met" x="0"/>
+        <item n="Open / Unresolved" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="17"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="49">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="48">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="41">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -3235,7 +3232,7 @@
     <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="11" count="0"/>
+          <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
@@ -3702,12 +3699,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
     </row>
     <row r="39" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
@@ -3938,20 +3935,20 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="E13" s="27" t="s">
+      <c r="B13" s="26"/>
+      <c r="E13" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="I13" s="28" t="s">
+      <c r="F13" s="26"/>
+      <c r="I13" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -4013,14 +4010,14 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="E23" s="27" t="s">
+      <c r="B23" s="26"/>
+      <c r="E23" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="F23" s="27"/>
+      <c r="F23" s="26"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>

--- a/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
+++ b/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/ticketing-system/reporting-and-kpis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="522" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD6885BA-3C94-4C38-A489-D352901DA6D7}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7925B0D4-437F-4789-B7EA-6336FC33CC87}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="1290" windowWidth="23475" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1290" windowWidth="23475" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="11" r:id="rId1"/>
@@ -687,7 +687,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -742,6 +742,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Heading 1" xfId="1" builtinId="16" hidden="1"/>
@@ -897,6 +898,54 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -918,6 +967,76 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -945,9 +1064,6 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color indexed="64"/>
@@ -1055,54 +1171,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -1124,76 +1192,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -1213,6 +1211,9 @@
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -2699,40 +2700,27 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A5:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E18:F20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item n="Not Escalated" x="0"/>
+        <item n="Escalated" x="1"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2743,26 +2731,14 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="5"/>
+    <field x="11"/>
   </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="5"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -2796,11 +2772,335 @@
     <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
+          <reference field="11" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item n="SLA Not Met" x="1"/>
+        <item n="SLA Met" x="0"/>
+        <item n="Open / Unresolved" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="17"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="30">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="39">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A5:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="48">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -2827,7 +3127,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I5:L10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="20">
@@ -2902,342 +3202,43 @@
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="31">
+    <format dxfId="58">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="55">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="54">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="51">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="49">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E18:F20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item n="Not Escalated" x="0"/>
-        <item n="Escalated" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="40">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="39">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="38">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="11" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item n="SLA Not Met" x="1"/>
-        <item n="SLA Met" x="0"/>
-        <item n="Open / Unresolved" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="17"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="49">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="48">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="47">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="46">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="45">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="44">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="43">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="42">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="41">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="58">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="57">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="56">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="55">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="54">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="53">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="52">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="51">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="50">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -3573,7 +3574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A55D82-B18D-478C-8743-BB6B0E9B43B7}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -3706,40 +3707,41 @@
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
     </row>
+    <row r="36" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="39" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
+      <c r="A39" s="5"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A33:D33"/>

--- a/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
+++ b/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/ticketing-system/reporting-and-kpis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7925B0D4-437F-4789-B7EA-6336FC33CC87}"/>
+  <xr:revisionPtr revIDLastSave="534" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4FEDA2B-8DF4-48C8-8EE1-28D4D3C7B894}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="1290" windowWidth="23475" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1290" windowWidth="23475" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="11" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="132">
   <si>
     <t>ticket_id</t>
   </si>
@@ -445,6 +445,9 @@
   </si>
   <si>
     <t>• One-third of ticket activity required escalation. Elevated escalation volume may indicate workflow dependencies or operational friction points.</t>
+  </si>
+  <si>
+    <t>• Ticket activity spans multiple departments, reinforcing the need for clear ownership and cross-functional coordination.</t>
   </si>
 </sst>
 </file>
@@ -736,13 +739,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Heading 1" xfId="1" builtinId="16" hidden="1"/>
@@ -989,54 +992,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -1058,76 +1013,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -1155,6 +1040,57 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color indexed="64"/>
@@ -1192,6 +1128,76 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -1211,9 +1217,6 @@
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -2700,8 +2703,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E18:F20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
@@ -2712,12 +2715,14 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item n="Not Escalated" x="0"/>
-        <item n="Escalated" x="1"/>
+      <items count="7">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2729,16 +2734,30 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="11"/>
+    <field x="9"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="6">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -2772,7 +2791,7 @@
     <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="11" count="0"/>
+          <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
@@ -2793,41 +2812,56 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A5:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item n="SLA Not Met" x="1"/>
-        <item n="SLA Met" x="0"/>
-        <item n="Open / Unresolved" x="2"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="17"/>
+    <field x="5"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="6">
+    <i>
+      <x v="5"/>
+    </i>
     <i>
       <x/>
     </i>
@@ -2836,6 +2870,12 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -2869,238 +2909,11 @@
     <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="17" count="0"/>
+          <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
     <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="39">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="38">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="31">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A5:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="48">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="47">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="46">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="45">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="44">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="43">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="42">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="41">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -3127,7 +2940,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I5:L10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="20">
@@ -3202,43 +3015,233 @@
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="58">
+    <format dxfId="40">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="37">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="36">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="33">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
+    <format dxfId="31">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E18:F20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item n="Not Escalated" x="0"/>
+        <item n="Escalated" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
     <format dxfId="49">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="48">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="11" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="41">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item n="SLA Not Met" x="1"/>
+        <item n="SLA Met" x="0"/>
+        <item n="Open / Unresolved" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="17"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="58">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="55">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="54">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="53">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="51">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -3707,7 +3710,7 @@
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
     </row>
-    <row r="36" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:4" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>110</v>
@@ -3936,21 +3939,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
+    <row r="13" spans="1:12" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="E13" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="F13" s="26"/>
-      <c r="I13" s="26" t="s">
+      <c r="B13" s="28"/>
+      <c r="E13" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="I13" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -4012,14 +4015,14 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="E23" s="26" t="s">
+      <c r="B23" s="28"/>
+      <c r="E23" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="F23" s="26"/>
+      <c r="F23" s="28"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>

--- a/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
+++ b/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
@@ -741,10 +741,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -810,54 +810,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -879,76 +831,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -976,6 +858,57 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color indexed="64"/>
@@ -1013,6 +946,76 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -1032,9 +1035,6 @@
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -2703,244 +2703,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="21">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="17">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="16">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A5:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="30">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="28">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="27">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="26">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="25">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3E0EE18-22CF-48BF-8A21-FC3CFB9322C4}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I5:L10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="20">
@@ -3015,42 +2777,42 @@
     <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="40">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="19">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="18">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="15">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="13">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3066,7 +2828,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0612E683-BE2F-4DB1-B66C-F4A6084D6199}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E18:F20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
@@ -3106,6 +2868,212 @@
     </i>
     <i>
       <x v="1"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="31">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="11" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item n="SLA Not Met" x="1"/>
+        <item n="SLA Met" x="0"/>
+        <item n="Open / Unresolved" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="17"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Ticket Count" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="40">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="39">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4283C0DB-D316-4062-937D-7849D5F5D8B6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -3139,7 +3107,7 @@
     <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="11" count="0"/>
+          <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
@@ -3160,41 +3128,56 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C81B2F50-164C-4AF1-98DA-5D67B6FE9F52}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3826521D-55DC-44D0-9B2F-69FA4EC77E75}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A5:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField numFmtId="22" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item n="SLA Not Met" x="1"/>
-        <item n="SLA Met" x="0"/>
-        <item n="Open / Unresolved" x="2"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="17"/>
+    <field x="5"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="6">
+    <i>
+      <x v="5"/>
+    </i>
     <i>
       <x/>
     </i>
@@ -3203,6 +3186,12 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -3236,7 +3225,7 @@
     <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="17" count="0"/>
+          <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
@@ -3244,6 +3233,17 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3703,12 +3703,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
     </row>
     <row r="36" spans="1:4" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
@@ -3940,20 +3940,20 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="E13" s="28" t="s">
+      <c r="B13" s="27"/>
+      <c r="E13" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="28"/>
-      <c r="I13" s="28" t="s">
+      <c r="F13" s="27"/>
+      <c r="I13" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -4015,14 +4015,14 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="E23" s="28" t="s">
+      <c r="B23" s="27"/>
+      <c r="E23" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="F23" s="28"/>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>

--- a/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
+++ b/ticketing-system/reporting-and-kpis/ticket-analysis-v1.xlsx
@@ -334,7 +334,7 @@
     <t>Open / Unresolved</t>
   </si>
   <si>
-    <t>Northstar Health Operations</t>
+    <t>Northstar Enterprise</t>
   </si>
   <si>
     <t>Operational KPI Highlights</t>
